--- a/novo projeto/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-03).xlsx
+++ b/novo projeto/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-03).xlsx
@@ -912,17 +912,17 @@
   </si>
   <si>
     <t>214
-181</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>R$ 870.654,28</t>
-  </si>
-  <si>
-    <t>R$ 4.558,40
-R$ 4.647,03</t>
+182</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>R$ 874.451,26</t>
+  </si>
+  <si>
+    <t>R$ 4.554,43
+R$ 4.642,36</t>
   </si>
   <si>
     <t>(3.9%)
@@ -935,10 +935,10 @@
     <t>(9.6%)</t>
   </si>
   <si>
-    <t>(14.8%)</t>
-  </si>
-  <si>
-    <t>(55.4%)</t>
+    <t>(14.2%)</t>
+  </si>
+  <si>
+    <t>(54.7%)</t>
   </si>
   <si>
     <t>3.9%</t>
@@ -950,7 +950,7 @@
     <t>26.8</t>
   </si>
   <si>
-    <t>74.2%</t>
+    <t>74.0%</t>
   </si>
   <si>
     <t>9.9%</t>
@@ -962,19 +962,19 @@
     <t>6.8</t>
   </si>
   <si>
-    <t>12.4</t>
+    <t>12.3</t>
   </si>
   <si>
     <t>18.8</t>
   </si>
   <si>
-    <t>73.0%</t>
-  </si>
-  <si>
-    <t>-R$ 28.288,85</t>
-  </si>
-  <si>
-    <t>2.97</t>
+    <t>72.9%</t>
+  </si>
+  <si>
+    <t>-R$ 28.390,15</t>
+  </si>
+  <si>
+    <t>2.95</t>
   </si>
   <si>
     <t>3.52</t>
@@ -8758,7 +8758,7 @@
         <v>19618</v>
       </c>
       <c r="B58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C58" s="4">
         <v>44</v>
@@ -8794,27 +8794,61 @@
       <c t="s" r="N58" s="4">
         <v>52</v>
       </c>
-      <c r="O58" s="5"/>
-      <c r="P58" s="5"/>
-      <c r="Q58" s="6"/>
-      <c r="R58" s="7"/>
-      <c r="S58" s="6"/>
-      <c r="T58" s="6"/>
-      <c r="U58" s="6"/>
-      <c r="V58" s="6"/>
-      <c r="W58" s="6"/>
-      <c r="X58" s="8"/>
-      <c r="Y58" s="6"/>
-      <c r="Z58" s="6"/>
-      <c r="AA58" s="8"/>
-      <c r="AB58" s="8"/>
+      <c r="O58" s="5">
+        <v>3796.98</v>
+      </c>
+      <c r="P58" s="5">
+        <v>3796.98</v>
+      </c>
+      <c r="Q58" s="6">
+        <v>-0.03846660318875228</v>
+      </c>
+      <c r="R58" s="7">
+        <v>43</v>
+      </c>
+      <c r="S58" s="6">
+        <v>-0.15686274509803921</v>
+      </c>
+      <c r="T58" s="6">
+        <v>1.2757555741668378</v>
+      </c>
+      <c r="U58" s="6">
+        <v>0.91898782716790717</v>
+      </c>
+      <c r="V58" s="6">
+        <v>0.019398574656700852</v>
+      </c>
+      <c r="W58" s="6">
+        <v>-0.0018920299817223162</v>
+      </c>
+      <c r="X58" s="8">
+        <v>31.288333333333334</v>
+      </c>
+      <c r="Y58" s="6">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="Z58" s="6">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="AA58" s="8">
+        <v>4.5898365853658536</v>
+      </c>
+      <c r="AB58" s="8">
+        <v>8.4355566666666668</v>
+      </c>
       <c r="AC58" s="8">
         <v>13.757220999999999</v>
       </c>
-      <c r="AD58" s="8"/>
-      <c r="AE58" s="6"/>
+      <c r="AD58" s="8">
+        <v>20.693333333333332</v>
+      </c>
+      <c r="AE58" s="6">
+        <v>0.46666666666666667</v>
+      </c>
       <c r="AF58" s="9"/>
-      <c r="AG58" s="5"/>
+      <c r="AG58" s="5">
+        <v>-101.3</v>
+      </c>
       <c r="AH58" s="10">
         <v>2</v>
       </c>
@@ -15457,7 +15491,7 @@
         <v>0</v>
       </c>
       <c r="AH111" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI111" s="11"/>
       <c r="AJ111" s="13">
@@ -15810,7 +15844,7 @@
         <v>-245.80000000000001</v>
       </c>
       <c r="AH114" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI114" s="11"/>
       <c r="AJ114" s="13">
@@ -16983,7 +17017,7 @@
         <v>0</v>
       </c>
       <c r="AH123" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI123" s="11"/>
       <c r="AJ123" s="13">
@@ -17376,7 +17410,7 @@
         <v>0</v>
       </c>
       <c r="AH126" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI126" s="11"/>
       <c r="AJ126" s="13">
@@ -18553,7 +18587,7 @@
         <v>0</v>
       </c>
       <c r="AH135" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI135" s="11"/>
       <c r="AJ135" s="13">
@@ -20857,7 +20891,7 @@
         <v>-3191.3499999999999</v>
       </c>
       <c r="AH153" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI153" s="11"/>
       <c r="AJ153" s="13">
@@ -22141,7 +22175,7 @@
         <v>-66.900000000000006</v>
       </c>
       <c r="AH163" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI163" s="11"/>
       <c r="AJ163" s="13">
@@ -24219,7 +24253,9 @@
       <c r="AB179" s="8">
         <v>0.88070000000000004</v>
       </c>
-      <c r="AC179" s="8"/>
+      <c r="AC179" s="8">
+        <v>3.8850859999999998</v>
+      </c>
       <c r="AD179" s="8">
         <v>10.852631578947367</v>
       </c>
@@ -28304,7 +28340,7 @@
       <c r="AF212" s="9"/>
       <c r="AG212" s="5"/>
       <c r="AH212" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI212" s="11"/>
       <c r="AJ212" s="12"/>
